--- a/ED_Streamlined_Theory.xlsx
+++ b/ED_Streamlined_Theory.xlsx
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>The field is withheld. At the discrete layer ED gets the integral Gauss law but not a determined local inverse-square field. The paper's own fork says you can have that field only by giving up either orientation-blindness or the arrow, which means leaving ED. | The winding is inert: it couples weakly and does not drive the stability landscape. | The quantization and the loop-independence were confirmed in the certified simulator to machine precision. The argument is structural; the simulation checks it. | The paper is strict that no charge spectrum was fitted. Reproducing the familiar ±1 and ∓⅓ pattern by fitting a topology to those values would violate its own discipline, and is not claimed.</t>
+          <t>The field is withheld. At the discrete layer ED gets the integral Gauss law but not a determined local inverse-square field. The paper's own fork says you can have that field only by giving up either orientation-blindness or the arrow, which means leaving ED. | The winding is inert: it couples weakly and does not drive the stability landscape. | What is protected, and what is not (scope added 2026-09-12). The integer cannot change while the loop that carries it exists. The loop is not itself protected: it is made of live participations, and where participation ceases there is no phase to difference and the number has nothing to be a property of, with nothing uncommitted. `Paper_ED_CCC` §3.6.1 turns on exactly this, using it to clear residual charge at the end of a cosmic aeon. The consequence is worth saying plainly: in this account charge is a property of a live loop around a thing, not of the thing alone. | The quantization and the loop-independence were confirmed in the certified simulator to machine precision. The argument is structural; the simulation checks it. | The paper is strict that no charge spectrum was fitted. Reproducing the familiar ±1 and ∓⅓ pattern by fitting a topology to those values would violate its own discipline, and is not claimed.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>the protection. Changing the winding would mean uncommitting a polarity</t>
+          <t>the protection. Changing the winding would mean uncommitting a polarity. This protects the number while its loop exists; it does not make the loop permanent</t>
         </is>
       </c>
     </row>

--- a/ED_Streamlined_Theory.xlsx
+++ b/ED_Streamlined_Theory.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Foundation'!$A$1:$G$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Results'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Results'!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Uses Map'!$A$1:$F$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dependencies'!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Papers'!$A$1:$D$19</definedName>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Event Density — the streamlined theory</t>
+          <t>Event Density — an honest account</t>
         </is>
       </c>
     </row>
@@ -512,14 +512,14 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>The part of Event Density that can be backed, in one file. Two halves: the 53 items ED starts from, and the 16 results that follow from them with nothing hidden added.</t>
+          <t>The core of Event Density in one file: the 53 items ED starts from, and the 16 results whose papers use nothing beyond them, each with a review verdict.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Built 2026-09-11 from Foundation.md and the sixteen result pages in this folder. Those documents are the source; this workbook is generated from them.</t>
+          <t>Generated from Foundation.md and the sixteen result pages in this folder. Those documents are the source.</t>
         </is>
       </c>
     </row>
@@ -529,73 +529,73 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>The tabs</t>
+          <t>The one thing to know up front</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Foundation — all 53 counted items plus the 3 uncounted definitions. Kind, name, plain statement, source paper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Results — the 16, one row each. Claim, strength, what it uses, what it borrows, what it leans on, how to kill it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Uses Map — one row per result-and-item pair. Filter by item key to see everything that uses a given assumption.</t>
+          <t>On review (2026-09-12), none of the sixteen derives anything not already known. Six are textbook results restated in ED terms, one is a modest ED-specific result, four are identifications without calculation, and five (all in the gravity block) rest on steps that do not hold as written. ED is an interpretive framework, not yet a theory that can be calculated from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>The tabs</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Dependencies — which results stand on earlier ED results, and where those stand.</t>
+          <t>Foundation — all 53 counted items plus the 3 uncounted definitions.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Papers — the 14 result papers and the 4 upstream papers.</t>
+          <t>Results — the 16, one row each: what the paper claims, the review verdict, what review found, what it uses, borrows and leans on, how to kill it.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Counts — live counts, recalculated from the other tabs.</t>
+          <t>Uses Map — one row per result-and-item pair. Filter by item key to see everything that uses a given assumption.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Not On This List — what was left out, and why.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>The rule</t>
+          <t>Dependencies — which results stand on earlier ED results, and where those stand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Papers — the 14 result papers and the 4 upstream papers. Each paper file opens with a review note that takes precedence over its text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Counts — live counts, including the review verdicts.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Everything here traces back to the Foundation tab. A result that needs an assumption not on that page does not belong on this list, however good the result is.</t>
+          <t>Not On This List — what was left out, and why.</t>
         </is>
       </c>
     </row>
@@ -605,14 +605,14 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>The one thing to know up front</t>
+          <t>What the verdicts mean</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Six of the sixteen pass through the same step: the emergent metric, whose lapse rests on a band-accounting premise that is argued rather than closed. If that premise fails, those six fall together. They are marked on the Dependencies tab.</t>
+          <t>Textbook result, restated: correct, but known physics or mathematics, with ED supplying vocabulary. Modest ED-specific result: a correct statement about an ED model with limited physical reach. Identification: a known phenomenon said to be a substrate object, with nothing calculated. Not established: relies on a step that does not hold as written.</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>What the strength words mean</t>
+          <t>The rule</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Follows from the foundation means the result needs nothing beyond the 53 items and standard mathematics. Where a result also borrows a tool or a value from published physics, the Results tab names it, so the borrowing is not hidden inside the word derived.</t>
+          <t>A result appears here only if its paper uses nothing beyond the Foundation tab. Passing the rule means no hidden assumptions; it does not make a result a derivation.</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>The canonical corpus is the ED Generative repository and its claims ledger, ED_ItemizedTheory_TieredClaims_v2.xlsx. Ledger row numbers on the Results tab point into that ledger.</t>
+          <t>The canonical corpus is the ED Generative repository and its claims ledger, ED_ItemizedTheory_TieredClaims_v2.xlsx. Ledger row numbers on the Results tab point into that ledger. The ledger's tiers predate this review.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>039 (May) takes the horizon's place from general relativity. GR-III (July) later showed the gravity rule builds a horizon by itself, with its size growing in step with the mass. The exact size, the 2 in 2GM/c², is still not pinned</t>
+          <t>039 (May) takes the horizon's place from general relativity. GR-III (July) has its linear gravity rule reach b = 0 on a surface whose size grows with the mass, but only because the solution is clipped at zero; that is not a strong-field result. The areal-coordinate Schwarzschild form the horizon results use is not derived (review, 2026-09-12)</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -2554,13 +2554,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -2570,6 +2570,7 @@
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="90" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2585,12 +2586,12 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>What the paper claims</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Verdict (review 2026-09-12)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
@@ -2636,6 +2637,11 @@
       <c r="M1" s="4" t="inlineStr">
         <is>
           <t>On the gravity chain</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>What review found</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2658,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>A black-hole horizon is the place where the links between inside and outside die off. The substrate stops carrying cross-chain content across it. This is a different kind of object from a geometric boundary, though the two sit in the same place.</t>
+          <t>The paper claims a black-hole horizon is where the substrate's links between inside and outside die off: a different kind of object from a geometric boundary, though in the same place.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with the horizon's location borrowed.</t>
+          <t>Identification, not a derivation. The horizon's location is taken from general relativity, and the collapse of cross-chain transport there is asserted, not computed.</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2680,17 +2686,17 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>The paper does not derive where the horizon sits. It takes that from general relativity and matches to it. | GR-III, written later, showed the gravity rule forms a horizon by itself, with its size growing in step with the mass. So part of what 039 borrows was later earned. The exact radius still is not pinned. | The identification of κ with the P12 gradient is a matching step, not a calculation.</t>
+          <t>The horizon's position comes from general relativity. | GR-III's rule produces a b = 0 surface whose size grows with mass, but only because its linear solution is clipped at zero. That is not a strong-field derivation of a horizon. | The identification of κ with the P12 gradient is a matching step, not a calculation.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>Detection of information-bearing Hawking radiation in a way inconsistent with V5 straddling the surface. Or analogue black-hole platforms producing Hawking-like radiation with no thermal (KMS) structure, which would break the mechanism rather than the location.</t>
+          <t>No practical test is identified. A substrate-level calculation showing that V5 transport does not vanish at r_H would remove the identification.</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the horizon's position, its area, or its temperature. Those are separate results. This is the claim about what a horizon *is* in the substrate.</t>
+          <t>Not a derivation of the horizon's position, its area or its temperature. It is a claim about what a horizon *is* in the substrate.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -2699,6 +2705,11 @@
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>The paper says openly that the horizon radius r_H is GR's (§3.2). Its ED content is the statement that the cross-bandwidth Γ_cross vanishes at that surface. Γ_cross is defined but never evaluated. | The surface gravity κ is matched to a "P12 gradient", not computed. | No practical test separates this from ordinary general relativity. An earlier version of this page offered analogue black holes as a test. They cannot probe a Planck-scale substrate: an analogue horizon's microphysics is that of its medium. That test has been removed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2713,12 +2724,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Near a horizon, the substrate's own cross-chain correlations become periodic in imaginary time, which is what "being at a temperature" means. The temperature is T = κ/2π.</t>
+          <t>The paper claims that near a horizon, the substrate's own cross-chain correlations become periodic in imaginary time, giving the temperature T = κ/2π.</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with the surface gravity and one standard tool borrowed.</t>
+          <t>Identification, not a derivation. T = κ/2π is the standard result, with κ borrowed. That ED's correlators carry the periodicity is asserted.</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2736,22 +2747,22 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>the imaginary-time (Euclidean) route to the 2π</t>
+          <t>the imaginary-time (Euclidean) route to the 2π; the surface gravity κ</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>ED's contribution here is that the *correlators* carry the periodicity, rather than matter fields on a fixed background. The 2π itself comes through the standard bridge. | The paper's separate prediction of a non-thermal correction of size (ω/ω_c)² rests on an extra assumption, P-V5-Even, that the kernel's envelope is symmetric in frequency. That assumption is not on the foundation page. It belongs to this paper only, and the temperature result does not need it.</t>
+          <t>The formula, κ and the periodicity all come from standard semiclassical physics. ED's addition is the claim that its correlators are what carry the periodicity. | The non-thermal correction rests on an extra postulate, P-V5-Even, that is not on the foundation page. The temperature result does not need it.</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>A substrate-level analysis showing the V5 correlators do not become periodic in imaginary time near the surface would take the temperature with it. The separate correction prediction dies if analogue experiments find a linear rather than quadratic deviation from thermal, or an enhancement rather than a suppression.</t>
+          <t>There is no distinctive test. A substrate calculation showing the V5 correlators are not periodic would remove the identification. The temperature itself stands or falls with standard semiclassical physics.</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Not a standalone derivation of the Hawking formula. The formula is standard; what ED supplies is a substrate object that satisfies it.</t>
+          <t>Not a derivation of the Hawking formula, and not a testable prediction beyond it.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -2760,11 +2771,16 @@
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Every input to the temperature is inherited: κ, the horizon's location, and the Euclidean periodicity. The paper's own audit marks its §3 steps as inherited. | That V5 correlators are periodic is asserted by appeal to coarse-graining (DCGT), not computed. | The paper's separate "headline" prediction has no fixed content. The prediction is a non-thermal correction of order (ω/ω_c)². Its cutoff is chosen (ω_c = c/ℓ_P), its parity is postulated (P-V5-Even) and its coefficient is undetermined. For any black hole well above the Planck mass it is unobservably small. | Analogue experiments cannot test that prediction. An analogue horizon's deviations from thermality come from its medium's dispersion (Unruh 1995 onward), not from a Planck-scale substrate. The analogue falsifier on the earlier version of this page has been removed.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Black-hole entropy: the coefficient 1/4</t>
+          <t>The black-hole entropy coefficient 1/4</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2774,12 +2790,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>A black hole's entropy is a quarter of its horizon area in Planck units, S = A/4. ED produces the 1/4, not just the area law.</t>
+          <t>The paper claims that ED produces the coefficient, not just the area law: a black hole's entropy is S = A/4 in Planck units, with both halves of the 1/4 coming from ED's own geometry.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with two borrowed tools.</t>
+          <t>Not established. The calculation is general relativity's own. It needs the exact Schwarzschild metric in areal coordinates and r_s = 2GM, and ED derives neither.</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -2797,22 +2813,22 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Euclidean continuation (turning time imaginary); the smoothness condition (no conical defect)</t>
+          <t>Euclidean continuation (turning time imaginary); the smoothness condition (no conical defect); the Schwarzschild metric in areal coordinates</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>The horizon shape comes from GR-III, whose lapse comes from GR-I. GR-III closes GR-I's α = 1 assumption only modulo a band-accounting premise. If that premise fails, this result falls with the rest of the gravity block. | The exact horizon radius, the 2 in 2GM/c², is not pinned. The simulations show a horizon forms and its size grows in step with the mass, which is all this derivation needs. | The 2π is obtained with a reversible-time device in a theory whose defining primitive is an irreversible arrow. The paper flags a substrate-native, continuation-free route as the genuine open frontier (§4b).</t>
+          <t>The horizon shape comes from GR-III, whose lapse comes from GR-I, and that lapse rests on a band-accounting premise that is argued rather than closed. | The areal-coordinate form of the metric and r_s = 2GM, neither derived (see "What review found"). | The 2π comes from a reversible-time device, used in a theory whose defining primitive is an irreversible arrow. The paper flags a continuation-free route as open, and its own attempt at one failed (§4b).</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>A demonstration that the rule's strong-coupling behaviour does not form a finite-radius horizon, or that the near-horizon geometry is not Rindler, would take the 1/4 with it. (GR-III §11.4; Thermal2Pi §2, which reports the numerical check b/(κρ)² → 1.)</t>
+          <t>A consistent derivation of ED's metric in a single coordinate form that is not Schwarzschild at second order would remove it. The isotropic form GR-I uses is already such a case.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the horizon's location from the substrate. Not a continuation-free derivation of the 2π. Not a claim to have gone beyond general relativity here: ED reads the 2π off the same near-horizon geometry GR does, and its addition is that the geometry itself is derived from the bandwidth rule rather than assumed.</t>
+          <t>Not a derivation of the 1/4 independent of general relativity. Not a derivation of the horizon's location. Not a continuation-free derivation of the 2π.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -2823,13 +2839,18 @@
       <c r="M4" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>The algebra is correct, and it is the standard Gibbons–Hawking calculation: continue to imaginary time, require no conical defect, read off T = κ/2π, integrate the first law. | S = A/4 needs two things GR-I does not derive: r_s = 2GM exactly, and A = 4πr_s². With r_s = kGM the first law gives S = A/(2k), so the 1/4 requires k = 2. That 2 comes from GR-I's identification b ∼ 1 + 2Φ, which matches the metric to Newtonian gravity; it is not derived. Together they are the Schwarzschild metric in areal-radius coordinates. GR-I builds its metric in isotropic form, g_ij = b⁻¹δ_ij. In that form the horizon area r²/b diverges at b = 0, and the second-order metric gives PPN β = 0, which observation excludes. The switch to the areal form is not justified. | A statement on this page was wrong. It said the exact horizon radius did not matter because a horizon forming at all "is all this derivation needs". The coefficient depends directly on that radius. | Net: ED reproduces GR's 1/4 by adopting GR's metric. It gives no independent derivation.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -2839,12 +2860,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>The gravitational waves left over from the early universe and the gravitational waves we detect today come from the same substrate process: fluctuations in the shape of the stability landscape. They are not two mechanisms that happen to look alike.</t>
+          <t>The paper claims that gravitational waves left over from the early universe and those detected today come from one substrate process, fluctuations in the shape of the stability landscape, rather than two mechanisms that look alike.</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, but its upstream has never been audited.</t>
+          <t>Identification, not a derivation. The paper's own audit has no derived steps; everything numerical is standard inflation and observational data.</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -2867,17 +2888,17 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>This is the weakest of the sixteen. The identification composes three upstream papers that are carried at M3 and have never been audited against the corpus: the saddle-classification paper, the gravitational-wave framework paper, and the saturation-regime paper. | Everything numerical is inherited. ED supplies no value here. | Until those three are read, this result should be quoted with that caveat attached.</t>
+          <t>Three unaudited upstream papers: saddle classification, the gravitational-wave framework and the saturation regime. | Everything numerical is inherited. ED supplies no value here.</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>A measured tensor-to-scalar ratio and inflation scale that cannot be reconciled with the substrate scaling. A significant violation of n_T = −r/8 would break the inherited half. Non-Gaussianity inconsistent with the fluctuation framework would break the ED half.</t>
+          <t>The tests listed in the paper (violation of n_T = −r/8, non-Gaussianity) test standard inflation, not ED. No ED-specific test is stated.</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Not a prediction of the primordial spectrum, and not a derivation of inflation. It is a claim that two things already described are the same thing.</t>
+          <t>Not a prediction of the primordial spectrum, and not a derivation of inflation.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -2886,11 +2907,16 @@
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Everything quantitative is standard. The scalar and tensor spectra, the slow-roll relations and every value come from standard inflation and Planck/BICEP data. | The ED content is naming. It calls tensor fluctuations "saddle-Hessian-signature fluctuations" and says present-day waves are the same thing. That rests on three upstream papers that are not in this repository and have never been audited. | There is no mechanism behind "same mechanism". ED builds no dynamics for gravitational waves (see ED's gravitational class).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Matter moves on geodesics</t>
+          <t>Geodesic motion</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2900,12 +2926,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>In ED, "matter is conserved" and "matter falls along the straightest available path" are the same statement. Free fall is not an extra law; it follows from the bookkeeping.</t>
+          <t>The paper claims that in ED, "matter is conserved" and "matter falls along the straightest available path" are the same statement.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, on top of ED's emergent metric.</t>
+          <t>Textbook result, restated in ED terms. For dust, covariant conservation and geodesic motion are equivalent in any metric theory. ED's own input, that its bandwidth current is that conserved current, is asserted.</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -2928,17 +2954,17 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Exact for dust. Pressure and anisotropic stress need the full dynamical rule, which this paper does not supply. | The metric it runs on comes from GR-I, whose lapse rests on a premise GR-III closes only modulo a band-accounting argument. Every gravity result here shares that exposure.</t>
+          <t>Exact for dust. Pressure and stress need dynamics that ED does not supply. | The conservation of the bandwidth current, which is asserted.</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>A demonstration that the substrate's bandwidth current is not the conserved flux this identification requires, or that its divergence for dust does not reduce to the geodesic condition, would remove the result. Empirically, any violation of the equivalence principle at leading order for pressureless matter.</t>
+          <t>Empirically, a leading-order violation of the equivalence principle for pressureless matter, which would also contradict general relativity. For ED specifically: showing the bandwidth current is not covariantly conserved.</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the full Einstein equations, and not a statement about matter with pressure.</t>
+          <t>Not a derivation of the Einstein equations, and not a new result. It is the standard identity, stated for ED's current.</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -2949,13 +2975,18 @@
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>The identity is standard: given ∇_μJ^μ = 0 with J = ρu, the divergence ∇_μ(ρu^μu^ν) equals ρa^ν, so conservation is equivalent to geodesic motion. This is true in general relativity and in any metric theory. | ED's input is asserted. GR-II §3.1 says the bandwidth current is covariantly conserved "by dual-flux typing". For light, the "discrete Fermat principle" is likewise asserted. | The metric this runs on is fixed only to first order (see the review note on GR-I).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is khronometric</t>
+          <t>ED's gravitational class</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -2965,12 +2996,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is not quite general relativity. It carries Einstein's two gravitational-wave modes plus one extra scalar, because the arrow of time is written into the law itself and picks out a preferred slicing of time.</t>
+          <t>The paper claims ED's gravity is khronometric: Einstein's two gravitational-wave modes plus one extra scalar, because the arrow of time written into the law picks out a preferred slicing of time.</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, as a structural count rather than a full computation.</t>
+          <t>Not established. The class is assumed, not derived. The only dynamics ED actually builds is a scalar diffusion equation, which has no waves and no tensor modes.</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -2993,17 +3024,17 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>The paper calls this structural, and says so plainly: it is an argument from the symmetry group, not a completed linearized calculation of the modes. | It is an infrared statement only. ED does not inherit the ultraviolet behaviour of other theories in this class. | The extra scalar's parameters are not computed in this paper.</t>
+          <t>The assumption that ED is a metric theory in this class. It is not shown from ED's dynamics. | The extra scalar's parameters are not computed.</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>A linearization of the dynamical rule that yields a different mode count, an extra vector mode for instance, would break the identification. So would the definite absence of any scalar gravitational-wave polarization at a sensitivity that excludes this mode, since the class requires one.</t>
+          <t>Constructing ED's dynamics for the metric and finding a different mode count. Empirically, excluding any scalar gravitational-wave polarization at the relevant sensitivity.</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Not a claim that ED is general relativity, and not a claim that it is a specific published alternative. It is a statement about which class the theory lands in, and why.</t>
+          <t>Not a derivation of ED's gravitational class. It is a conjecture about which class ED would fall into.</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -3014,13 +3045,18 @@
       <c r="M7" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>The count "2 tensor + 1 scalar" is borrowed, not derived. It is what khronometric gravity has. ED arrives at it by assuming it is a metric theory with a preferred foliation, then quoting the known count for that class. | ED's only built dynamics is a single scalar. GR-III's rule, ḃ = D∇²b − κρ, is first-order in time and describes one scalar. A disturbance e^{i(kx−ωt)} gives ω = −iDk²: it decays without travelling, so the rule has no waves at all. No tensor sector is ever constructed from it. | Lovelock's theorem has nothing to apply to. It needs field equations built from a metric, and ED has none. | What survives is a conjecture worth stating as one: that a fundamental arrow of time implies a preferred foliation.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Gravitational waves travel at the speed of light</t>
+          <t>Gravitational-wave speed</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -3030,12 +3066,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Gravitational waves and light share one speed, because they share one substrate and one transport. The 2017 neutron-star observation, which killed a long list of gravity theories, is an identity in ED rather than a constraint it has to satisfy.</t>
+          <t>The paper claims gravitational waves and light share one speed because they share one substrate and one transport, so the 2017 neutron-star observation is an identity in ED rather than a constraint.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, independent of the unbuilt parts of the rule.</t>
+          <t>Not established. The wave equation with speed c is written in by hand, and ED builds no dynamics for gravitational waves. Nature satisfies c_T = c, and ED is consistent with it by assumption.</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -3058,17 +3094,17 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>This does not depend on the unbuilt coefficients of the dynamical rule. The paper marks it independent of that residual, which makes it one of the sturdier gravity results. | It still sits on GR-I's metric, so it shares the gravity block's exposure to the band-accounting premise.</t>
+          <t>The existence of tensor waves travelling at the limiting speed, which is assumed. | The same argument implies that any Lorentz violation would affect all species equally. That holds only as far as the assumption does.</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>A measured difference between the tensor gravitational-wave speed and the speed of light beyond observational bounds. Or observation of Lorentz violation that differs between matter species at leading order, which would break the single-cone structure.</t>
+          <t>A measured difference between the speed of gravitational waves and the speed of light, which would also contradict general relativity.</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Not a new prediction. The observation is already in hand. The claim is that ED gets it for structural reasons rather than by choosing a parameter.</t>
+          <t>Not a new prediction, and not a derivation. ED is consistent with c_T = c by construction of its assumptions.</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -3079,13 +3115,18 @@
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>"One substrate, one cone" only sets a maximum speed. It limits how fast any signal can travel. It does not show that gravitational perturbations exist as waves, or that they travel at that maximum. | The wave equation is assumed. GR-III's propagating sector writes ḧ_ij = c²∇²h_ij directly. The rule GR-III actually builds is diffusive (ω = −iDk²), with no wave speed at all. | The observation is real (GW170817). ED's derivation of it is missing.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -3095,12 +3136,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>The extra scalar mode that ED's gravity carries moves at the speed of light, not at some other speed. Generic theories in this class allow a second, different cone. ED does not.</t>
+          <t>The paper claims the extra scalar mode ED's gravity carries travels at the speed of light, where generic theories in this class allow a second, different cone.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, at leading order.</t>
+          <t>Not established. The argument conflicts with the standard khronometric formula that GR-IV relies on.</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -3123,17 +3164,17 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Leading order only. GR-III says integrating out the dissipative reserve could shift the speed by a small amount, and does not compute how much. GR-IV files that as an open number, ε′, and notes it is one calculation, not two. | Shares the gravity block's dependence on the band-accounting premise.</t>
+          <t>A non-standard parametrization of the scalar speed. | It shares the gravity block's dependence on the band-accounting premise.</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>A scalar gravitational-wave polarization detected at a speed measurably different from light. Or a computation showing the reserve sector does supply a genuine kinetic term after all, which would restore a second cone.</t>
+          <t>It is already contradicted by the standard formula unless the tuning α = λ/(1+2λ) is derived. Empirically: a scalar gravitational-wave polarization moving at a speed measurably different from light.</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Not a claim about the size of the scalar mode or how easily it could be seen. The claim is only about its speed, and only at leading order.</t>
+          <t>Not an established result about ED's scalar mode.</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -3144,13 +3185,18 @@
       <c r="M9" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>GR-III's route: it gets c_s = c from the absence of a λθ² term, which means λ = 0. | The standard formula says otherwise. In the khronometric parametrization GR-IV uses (§3), with β = 0 the scalar speed is c_s² = λ(2−α)/α(2+3λ)]. With λ = 0 that gives zero, not c. | c_s = c needs a tuning. It requires α = λ/(1+2λ) with λ ≠ 0, and nothing in ED supplies that tuning. | The cited simulation doesn't bear on the question. It shows that a dissipative term damps a wave without changing its speed. That is true of damped waves in general and says nothing about ED's scalar in particular.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>The tightest preferred-frame test is passed exactly</t>
+          <t>The preferred-frame parameter α₂</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3160,12 +3206,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Theories with a preferred frame are usually killed by two numbers, α₁ and α₂, measured in the solar system and in pulsars. In ED, α₂ is exactly zero, for the same reason its two gravitational cones are both luminal.</t>
+          <t>The paper claims ED's preferred-frame parameter α₂ is exactly zero, because both of its gravitational cones are at the speed of light.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, at exactly the standing of the khronon-speed result.</t>
+          <t>Not established. The algebra is correct, but α₂ = 0 is the same equation as the khronon-speed condition, and that condition is itself not established.</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -3188,17 +3234,17 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>The paper flags this itself: the α₂ numerator and the luminal condition are one equation, not two facts. So α₂ = 0 carries exactly the standing of the khronon speed result and no more. | That standing is leading order. The uncomputed ε′ sets the size of any residual α₂. | A measured α₂ that is small and at the scale of ε′ would support this construction rather than break it. General relativity predicts exactly zero; ED predicts something of order ε′.</t>
+          <t>Both luminal conditions, neither derived for ED. | The uncomputed correction ε′ to the scalar speed.</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>A measured α₂ large compared with the renormalization scale. A measured α₁ at or above about 10⁻⁵ in any environment would break the companion suppression argument.</t>
+          <t>A measured α₂ well above the scale of ε′. But this is only meaningful once c_s = c is actually derived.</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Not an independent second success. It is the same causal-cone fact as the gravitational-wave speed, seen from another direction, and the paper says so.</t>
+          <t>Not an independent success, and not a result about ED until the luminal conditions are derived. What stands is a correct statement about khronometric gravity in general.</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -3209,13 +3255,18 @@
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>The algebra is correct and was checked against the literature. In khronometric gravity with β = 0, the α₂ numerator vanishes exactly when α = λ/(1+2λ). This is a true general statement: if both speeds are luminal, α₂ vanishes identically. | That condition is c_s = c, which is not established for ED (see the speed of the extra gravitational mode). | The companion α₁ estimate is not established either. GR-IV puts α₁ at about 10⁻⁹³ using the dimensional estimate λ_local ∼ ρ_event/ρ_Planck, which turns a constant coupling into a position-dependent field without changing the theory's action. | Couplings that small create a strong-coupling problem. Using the literature scaling √λ·M_P, a coupling of order 10⁻⁹³ puts the strong-coupling scale near 4×10⁻¹⁹ eV, so the theory would stop being perturbative at essentially every energy. The scaling is quoted, not re-derived.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3225,12 +3276,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>The structure group of a family of N indistinguishable channels is U(N), which is (SU(N) × U(1))/Z_N. Non-abelian gauge structure is not put in by hand; it is what having more than one channel means.</t>
+          <t>The paper claims a family of N indistinguishable channels has structure group U(N) = (SU(N) × U(1))/Z_N, so non-abelian gauge structure comes from having more than one channel, and the Standard Model's groups correspond to multiplicities {1, 2, 3}.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with one step in the paper left unnamed.</t>
+          <t>Textbook result, restated in ED terms. Norm-preserving invertible maps on C^N form U(N). The match to the Standard Model does not hold as stated.</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -3253,17 +3304,17 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>One step in the paper is not named as an assumption. "Invertibility between commitments" is what turns an isometry into a unitary. It is not one of the thirteen primitives, and given that the arrow makes commitment itself irreversible, it deserves a line of its own rather than a clause. | The paper as written said U(N) = SU(N) × U(1), which is not right as a group identity. Corrected to the quotient form on 2026-09-11. | The paper cited P08 for channel multiplicity, where the canonical primitive list puts channel structure at P07. Corrected the same day.</t>
+          <t>The unnamed invertibility step. | An assumed internal dimension d = 3 for the bound on N.</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>A stable fundamental gauge sector with N of 4 or more, since ED's stable families run to three. A parity-violating abelian force, since ED's abelian coupling is blind to handedness.</t>
+          <t>The linear-algebra step cannot fail. The physical claims attached to it already conflict with the Standard Model: hypercharge is chiral, and the group structure does not match.</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the Standard Model's gauge group. It says where groups of this shape come from, not which ones nature picked.</t>
+          <t>Not a derivation of the Standard Model's gauge group, and not a correct account of which groups appear.</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -3272,11 +3323,16 @@
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>The main step is standard linear algebra: U(N) is the group of norm-preserving transformations of C^N. | The multiplicities don't produce the Standard Model group. Multiplicities {1, 2, 3} give U(1) × U(2) × U(3), which has three abelian factors. The Standard Model group, (SU(3) × SU(2) × U(1))/Z₆, has one. | One kill condition was already met, and has been removed. The earlier version of this page listed "a parity-violating abelian force" as a way to kill the result. The Standard Model already has one: hypercharge U(1)_Y couples differently to left- and right-handed fermions. So the paper's claim that ED's abelian coupling is blind to handedness is contradicted by known physics. | The "no stable SU(N ≥ 4)" bound is assumed, not derived. It rests on an internal amplitude dimension d = 3 that the paper takes as given. | One step is unnamed. "Invertibility between commitments", which turns an isometry into a unitary, is not one of the primitives, and it sits awkwardly with the irreversibility of P11. | Two errors were corrected in the paper on 2026-09-11: the group identity, which still needed fixing in the paper's abstract and has now been fixed, and the primitive cited for channel multiplicity, which should have been P07 rather than P08.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3286,12 +3342,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Under a change of velocity, the substrate's position-type content stays put while its motion-type content transforms. That asymmetry is what puts the factor of one half into kinetic energy.</t>
+          <t>The paper claims that under a change of velocity, the substrate's position-type content stays put while its motion-type content transforms, and that this asymmetry puts the factor of one half into kinetic energy.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, on top of the emergent metric.</t>
+          <t>Textbook result, restated in ED terms. The 1/2 comes from the Taylor expansion of the relativistic energy, which the paper inherits. The substrate argument restates it.</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -3309,22 +3365,22 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>standard Galilean transformation theory; the relativistic starting point and the mass m</t>
+          <t>the relativistic energy E² = p²c² + m²c⁴ and its expansion; standard Galilean transformation theory; the mass m</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>The paper is explicit that the full Galilean group structure is open. The primitive it uses is necessary for the asymmetry, not sufficient for the whole group. | The paper corrected its own sourcing in September 2026: it had credited bandwidth with supplying the propagation sector, when bandwidth carries amount and transport carries rate.</t>
+          <t>The inherited Taylor expansion. | The paper itself says the full Galilean group structure is open.</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Detection of non-relativistic kinetic energy with a coefficient other than 1/2m. Substrate evidence that adjacency content does transform under a boost, or that propagation content does not.</t>
+          <t>A kinetic-energy coefficient other than 1/2 would contradict all of physics, not ED specifically. There is no ED-specific test.</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the Galilean group, and not a derivation of mass.</t>
+          <t>Not a derivation of the 1/2, the Galilean group or mass.</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -3333,6 +3389,11 @@
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>The argument is circular. Step 8 of the paper's audit imports E_kin = p²/2m from the expansion of √(p²c² + m²c⁴). The "Galilean Jacobian" steps then restate that result; they do not produce the 1/2 independently. | The adjacency/propagation split is vocabulary for position and momentum. The claim that it underlies x, p] = iħ is asserted.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3347,12 +3408,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>In 3+1 dimensions there is exactly one four-component spinor structure, up to a change of basis. Every way of writing the gamma matrices (Dirac, Weyl, Majorana) is the same object in different clothes, so nothing physical depends on which one is used.</t>
+          <t>In 3+1 dimensions there is exactly one four-component spinor structure up to a change of basis, so the Dirac, Weyl and Majorana forms of the gamma matrices are the same object written differently.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, using standard algebra.</t>
+          <t>Textbook result, restated in ED terms. This is Pauli's fundamental theorem on gamma matrices. ED assumes the dimension (P06) and inherits the signature.</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -3375,17 +3436,17 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>The signature arrives through the emergent metric rather than straight from the primitives, so this result inherits that machinery and its conditions. | The heavy lifting is standard mathematics. ED's content is that its own structure lands in this algebra at all.</t>
+          <t>The assumed dimension and the inherited signature.</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Evidence that the algebra admits inequivalent four-dimensional irreducible representations, which would contradict Pauli's theorem. Detection of spinor content in 3+1 dimensions that is not four-component. Evidence that the substrate permits a dimension other than 3+1.</t>
+          <t>Nothing here is specific to ED. The mathematics is settled, and the physical input, 3+1 dimensions, is assumed.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the Dirac equation, and not a claim that any particular basis is preferred.</t>
+          <t>Not a derivation of the Dirac equation, and not a derivation of the dimension of spacetime.</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -3394,6 +3455,11 @@
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>The result is correct. The heavy lifting is Pauli's theorem and Schur's lemma. | ED supplies no input beyond assuming 3+1 dimensions. The Lorentzian signature is inherited from another paper. | One minor error. The paper calls the choice between Cl(3,1) and Cl(1,3) a convention. That is true for complex representations, but as real algebras the two are not isomorphic, which matters for Majorana spinors. The uniqueness claim is unaffected. | The earlier kill conditions were mostly "Pauli's theorem is wrong". That is not a physical test.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3408,12 +3474,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>In three-dimensional space, swapping two identical things can only give a plus or a minus sign. Bosons and fermions exhaust the options. Anything in between needs two dimensions.</t>
+          <t>In three-dimensional space, exchanging two identical particles can only give a scalar phase of +1 or −1. Continuous exchange phases (anyons) need two dimensions.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, using standard topology. This is the cleanest of the sixteen.</t>
+          <t>Textbook result, restated in ED terms. It is correct: this is Leinaas–Myrheim (1977), with the spatial dimension assumed by P06.</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -3436,17 +3502,17 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Nothing beyond the three primitives and the standard mathematics. No paper-specific assumption, no borrowed value, no simulation. | The anyons seen in laboratory fractional quantum Hall systems are effectively two-dimensional. The paper treats them as consistent with this, not as a counterexample.</t>
+          <t>The assumed dimension, and standard mathematics.</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Detection of genuinely three-dimensional anyonic statistics, in the bulk rather than on a surface. Evidence that the substrate permits two spatial dimensions. Or a flaw in the standard topology result itself.</t>
+          <t>Nothing here is specific to ED. Genuinely three-dimensional anyons in the bulk of a material would contradict standard physics as well.</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Not a new prediction: physics has held this since 1977. It is a demonstration that ED reproduces it from its own starting point rather than assuming it.</t>
+          <t>Not a new prediction, and not a derivation of why space has three dimensions.</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -3455,6 +3521,11 @@
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>The mathematics is correct, and ED adds nothing to it beyond assuming three spatial dimensions. | The claim was overstated. The earlier version of this page said bosons and fermions "exhaust the options". That holds for scalar phases only. Topology does not exclude the higher-dimensional representations of the permutation group (parastatistics). | It is "cleanest" only because nothing ED-specific is in it. The earlier version called this the cleanest of the sixteen, and it is, for that reason.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3469,12 +3540,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>The substrate carries an integer that cannot change: how many times the polarity angle winds around a closed loop. It is exactly quantized, it is conserved, and the arrow is what protects it. That integer is the skeleton of electric charge.</t>
+          <t>A U(1) polarity angle committed single-valued around a closed loop winds a whole number of times, and that number cannot change while the loop exists. The paper reads it as the topological skeleton of electric charge.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with the field itself still missing.</t>
+          <t>Textbook result, restated in ED terms. The integer winding of a U(1) phase around a loop is standard topology. The paper adds an honest negative result about the field.</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -3497,17 +3568,17 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>The field is withheld. At the discrete layer ED gets the integral Gauss law but not a determined local inverse-square field. The paper's own fork says you can have that field only by giving up either orientation-blindness or the arrow, which means leaving ED. | The winding is inert: it couples weakly and does not drive the stability landscape. | What is protected, and what is not (scope added 2026-09-12). The integer cannot change while the loop that carries it exists. The loop is not itself protected: it is made of live participations, and where participation ceases there is no phase to difference and the number has nothing to be a property of, with nothing uncommitted. `Paper_ED_CCC` §3.6.1 turns on exactly this, using it to clear residual charge at the end of a cosmic aeon. The consequence is worth saying plainly: in this account charge is a property of a live loop around a thing, not of the thing alone. | The quantization and the loop-independence were confirmed in the certified simulator to machine precision. The argument is structural; the simulation checks it. | The paper is strict that no charge spectrum was fitted. Reproducing the familiar ±1 and ∓⅓ pattern by fitting a topology to those values would violate its own discipline, and is not claimed.</t>
+          <t>No field. At the discrete layer there is no determined local field. The paper's fork shows one appears only by giving up both orientation-blindness and the arrow. | Inert winding. It couples only weakly and does not drive the stability landscape. | Live loops. The integer cannot change while its loop exists, but the loop itself is not protected. In this account charge is a property of a live loop around a thing. | No charge spectrum. None is produced: no ±1, no ∓⅓.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>A demonstration that the committed holonomy is not quantized to integers, or that the winding can change without an uncommitting. A measurement showing the circulation is not loop-independent. Or a determined local inverse-square field produced while keeping both orientation-blindness and the arrow.</t>
+          <t>The integer winding itself cannot fail. The ED-specific claim at risk is the negative result: obtaining a determined local 1/r² field while keeping both orientation-blindness and the arrow would overturn it.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of electric charge, its spectrum, or Coulomb's law. It is the skeleton: an exact, protected, conserved integer of the right shape.</t>
+          <t>Not a derivation of electric charge, its values or Coulomb's law.</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -3516,6 +3587,11 @@
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>The winding is an integer by construction. π₁(U(1)) = ℤ, so for a single-valued phase the result is exact. The simulation's "machine precision" check could not have failed. | "Integral Gauss law" is an analogy. The fact that the winding doesn't depend on which loop you take is the ordinary vortex winding of the XY / lattice U(1) model. Gauss's law counts the flux of a field, and here there is no field, as the paper itself says. | "Protected by the arrow" is an interpretation, not a separate result. | What holds up is the fork, a real and honestly reported negative: a determined 1/r² field appears only when both orientation-blindness and irreversibility are dropped, that is, only by leaving ED.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3530,12 +3606,12 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>A substrate whose rules do not favour a handedness cannot produce a handed transport, for any number of channels. So the handedness of the weak force cannot be written into ED's law. It has to be a broken symmetry: a choice the universe made, not a rule it follows.</t>
+          <t>The paper claims that a substrate whose rules do not favour a handedness cannot produce a handed transport, for any number of channels. So parity violation cannot be written into ED's law; it has to be a broken symmetry.</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, at the transport level only.</t>
+          <t>Modest ED-specific result. The theorem is correct, but it is the statement that a parity-symmetric model carries no parity-odd invariant, and one claim in the paper conflicts with Standard Model hypercharge.</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -3553,22 +3629,22 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>representation theory, for which channel-count is chiral in the Standard Model</t>
+          <t>representation theory, for which forces are chiral in the Standard Model; the point-gap winding as the chirality invariant</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Transport level only. The step from substrate transport down to a genuine Dirac sector is open, and the paper says so. Everything here is contingent on that descent. | Which channel-count ends up chiral is inherited from representation theory, not produced by ED. The pattern in the Standard Model matches no transport winding. | The anomaly-freedom corollary rides on the same open descent.</t>
+          <t>Transport level only. The step from substrate transport to a genuine Dirac sector is open. | The model form. Everything rests on ED's substrate having this commitment-map form.</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>A parity-clean commitment map shown to carry a nonzero winding for some channel-count, which would be a chiral coupling without breaking the symmetry. A construction that fixes which channel-count is chiral from ED's own dynamics, which would overturn the "inherited casting" verdict. Evidence that handedness is a fixed law-level property rather than a contingent choice.</t>
+          <t>A parity-symmetric map of this form with nonzero winding is mathematically impossible, so the theorem itself cannot fail. The physical claim fails if ED's substrate is not parity-symmetric in this form, or if handedness is shown to be a fixed property of the law.</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the weak force's handedness, and not a derivation of the Standard Model's matter content.</t>
+          <t>Not a derivation of the weak force's handedness, or of the Standard Model's matter content.</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -3577,11 +3653,16 @@
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>The theorem is correct. For a parity-symmetric one-way hopping map H(k) = e^{ik}A + e^{−ik}SAS⁻¹, det H(k) is even in k, so the point-gap winding is zero for every channel count. | Its content is modest. As the paper itself says, it is "parity symmetry forbids a parity-odd invariant" applied to this model. The physical content lies in whether ED's substrate has this form. | One claim misidentifies the abelian factor. The paper says "N = 1 is forced vector, matching electromagnetism". The Standard Model's fundamental abelian factor is hypercharge, and hypercharge is chiral. | Two claims are unsupported. Offering the pseudoreality of SU(2) as the origin of the weak force's chirality is speculation. The paper's distinctive prediction, that handedness is spontaneous and correlated with the matter/antimatter sign, has no stated way to measure it.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3591,12 +3672,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Black-hole horizons, acceleration horizons, the cosmological horizon and acoustic horizons in fluids are the same substrate object seen four ways: a surface where cross-chain content saturates and stops. They all carry T = κ/2π for that reason.</t>
+          <t>The paper claims that black-hole horizons, acceleration horizons, the cosmological horizon and acoustic horizons in fluids are the same substrate object seen four ways: a surface where cross-chain content saturates and stops.</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>follows from the foundation, with all four temperatures borrowed.</t>
+          <t>Identification, not a derivation. Every number is standard physics, and the paper's own audit marks the identification as a position.</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -3619,17 +3700,17 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>ED's own content is the identification, not the formula. Everything numerical is standard. | The paper carries this as M3, a structural identification, not a derivation. | Two of the four cases (cosmological, acoustic) arrive through further inheritance chains rather than direct substrate construction.</t>
+          <t>ED's content is the identification alone. Everything numerical is standard. | Two of the four cases, cosmological and acoustic, arrive through further chains of inherited results.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>A horizon-class object that does not show the universal thermal spectrum. Or substrate evidence that cross-chain saturation does not occur at one of the four. A fifth horizon class would extend the picture rather than break it.</t>
+          <t>There is no distinctive test. A horizon without a thermal spectrum would break the standard formula, not ED specifically.</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Not a derivation of the Hawking-Unruh formula, and not a prediction of any of the four temperatures.</t>
+          <t>Not a derivation of the Hawking–Unruh formula, and not a prediction of any of the four temperatures.</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -3638,9 +3719,14 @@
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>The shared temperature law is standard physics. The four temperatures and surface gravities come from Hawking, Unruh, Gibbons–Hawking and Unruh's acoustic analogue, and their shared law is textbook. | The shared substrate mechanism is claimed, not calculated. It is not worked out for any of the four cases. | The acoustic case has no testable content. A fluid's horizon lives far above the substrate scale, so calling it "the same substrate object" predicts nothing.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:N17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3900,7 +3986,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>one-way crossing; the gradient that becomes surface gravity</t>
+          <t>one-way crossing; the gradient identified with surface gravity</t>
         </is>
       </c>
     </row>
@@ -3930,7 +4016,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>one-way crossing; the gradient that becomes surface gravity</t>
+          <t>one-way crossing; the gradient identified with surface gravity</t>
         </is>
       </c>
     </row>
@@ -3960,7 +4046,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>the cross-chain kernel whose transport dies off</t>
+          <t>the cross-chain kernel whose transport is said to die off</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4346,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>the correlators that carry the thermal structure</t>
+          <t>the correlators said to carry the thermal structure</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4383,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Black-hole entropy: the coefficient 1/4</t>
+          <t>The black-hole entropy coefficient 1/4</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -4323,7 +4409,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -4346,14 +4432,14 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>the fluctuating structure, and the symmetry behind the conserved quantities</t>
+          <t>the fluctuating structure, and the symmetry behind conserved quantities</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -4376,14 +4462,14 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>the fluctuating structure, and the symmetry behind the conserved quantities</t>
+          <t>the fluctuating structure, and the symmetry behind conserved quantities</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -4406,14 +4492,14 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>the landscape whose shape fluctuates</t>
+          <t>the landscape whose shape is said to fluctuate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -4436,14 +4522,14 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>the landscape whose shape fluctuates</t>
+          <t>the landscape whose shape is said to fluctuate</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -4466,14 +4552,14 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>the landscape whose shape fluctuates</t>
+          <t>the landscape whose shape is said to fluctuate</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -4496,14 +4582,14 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>the landscape whose shape fluctuates</t>
+          <t>the landscape whose shape is said to fluctuate</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -4526,14 +4612,14 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>the landscape whose shape fluctuates</t>
+          <t>the landscape whose shape is said to fluctuate</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -4563,7 +4649,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Matter moves on geodesics</t>
+          <t>Geodesic motion</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -4586,14 +4672,14 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>makes the bandwidth current an extensive, conserved flux</t>
+          <t>offered as the reason the bandwidth current is an extensive, conserved flux</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Matter moves on geodesics</t>
+          <t>Geodesic motion</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -4616,14 +4702,14 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>types the current as a transported amount, which fixes what kind of object it is</t>
+          <t>offered as fixing what kind of object the current is</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is khronometric</t>
+          <t>ED's gravitational class</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -4646,14 +4732,14 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>puts the time direction in the dynamics, not in the starting conditions</t>
+          <t>offered as putting the time direction in the dynamics</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is khronometric</t>
+          <t>ED's gravitational class</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -4676,14 +4762,14 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>supplies the slicing</t>
+          <t>offered as supplying the slicing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is khronometric</t>
+          <t>ED's gravitational class</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -4713,7 +4799,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Gravitational waves travel at the speed of light</t>
+          <t>Gravitational-wave speed</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -4743,7 +4829,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Gravitational waves travel at the speed of light</t>
+          <t>Gravitational-wave speed</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -4766,14 +4852,14 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>fixes the finite width that sets the speed limit</t>
+          <t>the finite width that sets the speed limit</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -4796,14 +4882,14 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>makes the commitment-reserve sector one-way, a drain that never refills</t>
+          <t>offered as making the reserve sector one-way</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -4833,7 +4919,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -4863,7 +4949,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -4893,7 +4979,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>The tightest preferred-frame test is passed exactly</t>
+          <t>The preferred-frame parameter α₂</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -4919,7 +5005,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -4942,14 +5028,14 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>forces transport to preserve the norm, which makes it an isometry</t>
+          <t>forces transport to preserve the norm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -4979,7 +5065,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -5009,7 +5095,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -5032,14 +5118,14 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>cross-channel mixing, which is the non-abelian part</t>
+          <t>cross-channel mixing, the non-abelian part</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -5062,14 +5148,14 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>single-channel transport, which is the abelian part</t>
+          <t>single-channel transport, the abelian part</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -5099,7 +5185,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -5122,14 +5208,14 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>makes adjacency content boost-invariant</t>
+          <t>offered as making position content boost-invariant</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -5152,14 +5238,14 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>supplies the motion-rate content, which does transform</t>
+          <t>the motion-rate content, which transforms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -5182,14 +5268,14 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>supplies only the non-negative size of that content</t>
+          <t>only the non-negative size of that content</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -5219,7 +5305,7 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -5242,14 +5328,14 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>it runs on the emergent metric, so those conditions apply</t>
+          <t>it runs on the emergent metric</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -5272,14 +5358,14 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>it runs on the emergent metric, so those conditions apply</t>
+          <t>it runs on the emergent metric</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -5302,14 +5388,14 @@
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>it runs on the emergent metric, so those conditions apply</t>
+          <t>it runs on the emergent metric</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -5332,14 +5418,14 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>it runs on the emergent metric, so those conditions apply</t>
+          <t>it runs on the emergent metric</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -5362,7 +5448,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>it runs on the emergent metric, so those conditions apply</t>
+          <t>it runs on the emergent metric</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5478,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>load-bearing. It forces the signature, and so fixes which Clifford algebra applies</t>
+          <t>fixes which Clifford algebra applies</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5568,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>the angular structure carried onto the gammas</t>
+          <t>the angular structure</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5598,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>supplies the spinor carriers</t>
+          <t>the spinor carriers</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5628,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>the signature comes through the emergent metric, which needs this condition held</t>
+          <t>the signature comes through the emergent metric</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5658,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>the load-bearing item. Everything turns on the dimension being three</t>
+          <t>the one input the theorem needs</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5688,7 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>supplies the identical carriers being exchanged</t>
+          <t>the identical carriers being exchanged</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5808,7 @@
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>the protection. Changing the winding would mean uncommitting a polarity. This protects the number while its loop exists; it does not make the loop permanent</t>
+          <t>read as the protection; changing the winding would mean uncommitting a polarity</t>
         </is>
       </c>
     </row>
@@ -5812,14 +5898,14 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>one of the two factors in the handedness operator</t>
+          <t>the one-way hop</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -5849,7 +5935,7 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -5879,7 +5965,7 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -5909,7 +5995,7 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -5939,7 +6025,7 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
@@ -5962,14 +6048,14 @@
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>the kernel that saturates</t>
+          <t>the kernel said to saturate</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
@@ -5999,7 +6085,7 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -6029,7 +6115,7 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
@@ -6059,7 +6145,7 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
@@ -6089,7 +6175,7 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -6177,14 +6263,14 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>κ is borrowed, not computed</t>
+          <t>an identification; κ and location borrowed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Black-hole entropy: the coefficient 1/4</t>
+          <t>The black-hole entropy coefficient 1/4</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -6199,14 +6285,14 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>built from the primitives, but through GR-I's lapse, which rests on the band-accounting premise (see "What this leans on")</t>
+          <t>the linear rule clipped at b = 0; passes through GR-I's lapse, which rests on the band-accounting premise; the areal-coordinate reading is not derived</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Black-hole entropy: the coefficient 1/4</t>
+          <t>The black-hole entropy coefficient 1/4</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -6216,19 +6302,19 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>the relation between the two metric parts, g₀₀g_rr = −1</t>
+          <t>the relation g₀₀g_rr = −1</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>same chain</t>
+          <t>holds in areal coordinates only, which GR-I does not establish (see its review note)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Matter moves on geodesics</t>
+          <t>Geodesic motion</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -6243,14 +6329,14 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>rests on the band-accounting premise (see below)</t>
+          <t>first order only; rests on the band-accounting premise</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ED's gravity is khronometric</t>
+          <t>ED's gravitational class</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -6265,14 +6351,14 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>rests on the band-accounting premise</t>
+          <t>first order only; rests on the band-accounting premise</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Gravitational waves travel at the speed of light</t>
+          <t>Gravitational-wave speed</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -6287,19 +6373,19 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>rests on the band-accounting premise</t>
+          <t>first order only; rests on the band-accounting premise</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>the khronometric class (GR-II)</t>
+          <t>ED's gravitational class (GR-II)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -6309,14 +6395,14 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>structural count</t>
+          <t>assumed, not derived</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -6331,36 +6417,36 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>rests on the band-accounting premise</t>
+          <t>first order only; rests on the band-accounting premise</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>The tightest preferred-frame test is passed exactly</t>
+          <t>The preferred-frame parameter α₂</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>gravity waves at c</t>
+          <t>gravitational-wave speed</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>one of the two luminal conditions</t>
+          <t>c_T = c (β = 0)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>independent of the unbuilt rule coefficients, but sits on GR-I's metric and so on the band-accounting premise</t>
+          <t>assumed, not derived; sits on GR-I's metric and the band-accounting premise</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>The tightest preferred-frame test is passed exactly</t>
+          <t>The preferred-frame parameter α₂</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -6370,19 +6456,19 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>the other</t>
+          <t>the tuning α = λ/(1+2λ)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>leading order, with an uncomputed correction ε′; also rests on the band-accounting premise</t>
+          <t>not established; conflicts with the standard formula as argued in GR-III</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -6397,14 +6483,14 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>location borrowed</t>
+          <t>an identification; location borrowed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -6419,7 +6505,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>2π borrowed</t>
+          <t>an identification; standard formula</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6565,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Why kinetic energy has a 1/2 in it</t>
+          <t>The 1/2 in kinetic energy</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
@@ -6519,7 +6605,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Four kinds of horizon, one law</t>
+          <t>Four kinds of horizon as one object</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -6599,7 +6685,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>The extra gravitational mode also travels at c</t>
+          <t>The speed of the extra gravitational mode</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
@@ -6619,7 +6705,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Matter moves on geodesics; ED's gravity is khronometric; Gravitational waves travel at the speed of light</t>
+          <t>Geodesic motion; ED's gravitational class; Gravitational-wave speed</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -6639,7 +6725,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>The tightest preferred-frame test is passed exactly</t>
+          <t>The preferred-frame parameter α₂</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -6699,7 +6785,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Primordial gravitational waves and today's are one mechanism</t>
+          <t>Primordial and present-day gravitational waves</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -6719,7 +6805,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Where the gauge groups come from</t>
+          <t>Gauge groups and channel multiplicity</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -6739,7 +6825,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Black-hole entropy: the coefficient 1/4</t>
+          <t>The black-hole entropy coefficient 1/4</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -6838,7 +6924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7020,6 +7106,60 @@
       </c>
       <c r="B18" s="10">
         <f>SUMPRODUCT((Results!$B$2:$B$17&lt;&gt;"")/COUNTIF(Results!$B$2:$B$17,Results!$B$2:$B$17&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Review verdicts (2026-09-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Textbook result, restated</t>
+        </is>
+      </c>
+      <c r="B21" s="10">
+        <f>COUNTIF(Results!$D:$D,"Textbook result*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Modest ED-specific result</t>
+        </is>
+      </c>
+      <c r="B22" s="10">
+        <f>COUNTIF(Results!$D:$D,"Modest*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Identification, not a derivation</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>COUNTIF(Results!$D:$D,"Identification*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Not established</t>
+        </is>
+      </c>
+      <c r="B24" s="10">
+        <f>COUNTIF(Results!$D:$D,"Not established*")</f>
         <v/>
       </c>
     </row>
@@ -7070,7 +7210,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Holds given a further local assumption that is not on the foundation page. Real work, honestly labelled, but outside this list.</t>
+          <t>Holds given a further local assumption that is not on the foundation page. Outside this list.</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7345,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Nine in the ledger, eight of them on this list. Row 42 (the c-power in G) is excluded as unit arithmetic.</t>
+          <t>Nine in the ledger, eight of them on this list. Row 42 (the c-power in G) is excluded as unit arithmetic. Review of 2026-09-12: none of the eight holds as a derivation of new content; see the Results tab.</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7375,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>All eight are on this list.</t>
+          <t>All eight are on this list. Review of 2026-09-12: these are mostly known results restated; see the Results tab.</t>
         </is>
       </c>
     </row>

--- a/ED_Streamlined_Theory.xlsx
+++ b/ED_Streamlined_Theory.xlsx
@@ -2843,7 +2843,7 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>The algebra is correct, and it is the standard Gibbons–Hawking calculation: continue to imaginary time, require no conical defect, read off T = κ/2π, integrate the first law. | S = A/4 needs two things GR-I does not derive: r_s = 2GM exactly, and A = 4πr_s². With r_s = kGM the first law gives S = A/(2k), so the 1/4 requires k = 2. That 2 comes from GR-I's identification b ∼ 1 + 2Φ, which matches the metric to Newtonian gravity; it is not derived. Together they are the Schwarzschild metric in areal-radius coordinates. GR-I builds its metric in isotropic form, g_ij = b⁻¹δ_ij. In that form the horizon area r²/b diverges at b = 0, and the second-order metric gives PPN β = 0, which observation excludes. The switch to the areal form is not justified. | A statement on this page was wrong. It said the exact horizon radius did not matter because a horizon forming at all "is all this derivation needs". The coefficient depends directly on that radius. | Net: ED reproduces GR's 1/4 by adopting GR's metric. It gives no independent derivation.</t>
+          <t>The algebra is correct, and it is the standard Gibbons–Hawking calculation: continue to imaginary time, require no conical defect, read off T = κ/2π, integrate the first law. | S = A/4 needs two things GR-I does not derive: r_s = 2GM exactly, and A = 4πr_s². Together they are the Schwarzschild metric in areal-radius coordinates. With r_s = kGM the first law gives S = A/(2k), so the 1/4 requires k = 2; that 2 comes from GR-I's identification b ∼ 1 + 2Φ, which matches the metric to Newtonian gravity rather than deriving it. GR-I builds its metric in isotropic form, g_ij = b⁻¹δ_ij. In that form the horizon area r²/b diverges at b = 0, and the second-order metric gives PPN β = 0, which observation excludes. The switch to the areal form is not justified. | A statement on this page was wrong. It said the exact horizon radius did not matter because a horizon forming at all "is all this derivation needs". The coefficient depends directly on that radius. | Net: ED reproduces GR's 1/4 by adopting GR's metric. It gives no independent derivation.</t>
         </is>
       </c>
     </row>
